--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -518,6 +518,9 @@
       <c r="C11" t="str">
         <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -576,7 +579,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08683888580</v>
+        <v>086838885810</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -522,9 +522,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F15" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>111_绣球紫粉_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -579,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>086838885810</v>
+        <v>0868388858102102015201525850</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -604,6 +604,9 @@
       <c r="C21" t="str">
         <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -662,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0868388858102102015201525850</v>
+        <v>0868388858102102015201525855</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -608,9 +608,92 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>3</v>
+      </c>
+      <c r="C26" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -665,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0868388858102102015201525855</v>
+        <v>0868388858102102015201525855161261014255100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -690,6 +690,9 @@
       <c r="A31" t="str">
         <v>4</v>
       </c>
+      <c r="C31" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -693,6 +693,9 @@
       <c r="C31" t="str">
         <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -751,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0868388858102102015201525855161261014255100</v>
+        <v>08683888581021020152015258551612610142551010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-10.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,9 +697,60 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>774_紫娇花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>5</v>
+      </c>
+      <c r="C37" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -754,7 +805,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08683888581021020152015258551612610142551010</v>
+        <v>08683888581021020152015258551612610142551010105050201010</v>
       </c>
     </row>
   </sheetData>
